--- a/legal_forms/001_holistic_mastery_agreement--legal_forms.xlsx
+++ b/legal_forms/001_holistic_mastery_agreement--legal_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,11 +437,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E43"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -525,13 +525,13 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>First page</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -548,13 +548,13 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>name</t>
+          <t>Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -571,13 +571,13 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>Email</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -594,13 +594,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>contact_number</t>
+          <t>Contact Number</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -617,20 +617,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>contact_number_2</t>
+          <t>Address</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -640,20 +640,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>address</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -663,13 +663,13 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>address_2</t>
+          <t>Time of Birth</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -686,13 +686,13 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>Date of Termination</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -709,20 +709,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>time_of_birth</t>
+          <t>Time of Termination</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -732,20 +732,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>email_field</t>
+          <t>Date of Signature</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -755,20 +755,20 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>contact_number_3</t>
+          <t>Time of Signature</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -778,20 +778,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>address_3</t>
+          <t>Signature</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -801,20 +801,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>date_of_termination</t>
+          <t>First Page Item 12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>time_of_termination</t>
+          <t>Second Page</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>first_page_item_14</t>
+          <t>second_page</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>terms</t>
+          <t>Second Page (2)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -860,17 +860,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>first_page_item_15</t>
+          <t>second_page_item</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>date_of_terms</t>
+          <t>Second Page Item</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -883,17 +883,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>first_page_item_16</t>
+          <t>second_page_item_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>time_of_terms</t>
+          <t>Second Page Item 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -906,527 +906,21 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>first_page_item_17</t>
+          <t>second_page_item_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>termination_date</t>
+          <t>Second Page Item 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>first_page_item_18</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>termination_time</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>second_page</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Second page</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>second_page_item</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>second_page_item_2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>second_page_item_3</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>contact_number</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>second_page_item_4</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>contact_number_2</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>second_page_item_5</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>address</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>second_page_item_6</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>address_2</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>second_page_item_7</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>date_of_birth</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>second_page_item_8</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>time_of_birth</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>date_of_termination</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Date of Termination</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>time_of_termination</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Time of Termination</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>termination_date</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Termination Date</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>termination_time</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Termination Time</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>second_page_item_9</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>signature</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>second_page_item_10</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>date_of_signature</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>time_of_signature</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Time Of Signature</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>date_of_signature_2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Date Of Signature 2</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>time_of_signature_2</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Time Of Signature 2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>second_page_item_11</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>terms</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>date_of_terms</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Date of Terms</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>time_of_terms</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Time of Terms</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1443,12 +937,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1471,49 +965,117 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>second_page_item_9_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>signature_1</t>
+          <t>name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Signature 1</t>
+          <t>Name</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>second_page_item_9_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>signature_2</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Signature 2</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>second_page_item_9_choices</t>
+          <t>first_page_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Contact Number</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>first_page_choices</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>address</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Address</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>first_page_item_11_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>signature_1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Signature 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>first_page_item_11_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>signature_2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Signature 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>first_page_item_11_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>signature_3</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Signature 3</t>
         </is>
